--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table37.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table37.xlsx
@@ -130,7 +130,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -151,18 +151,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -471,7 +472,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -490,24 +491,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -524,7 +525,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
@@ -539,7 +540,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
@@ -554,7 +555,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -571,7 +572,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="3"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
@@ -586,7 +587,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
@@ -601,7 +602,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -618,7 +619,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -633,7 +634,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3"/>
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
@@ -648,7 +649,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -665,7 +666,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="3"/>
+      <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -680,7 +681,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -695,7 +696,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -712,7 +713,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="3"/>
+      <c r="A15" s="4"/>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
@@ -727,7 +728,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="3"/>
+      <c r="A16" s="4"/>
       <c r="B16" s="1" t="s">
         <v>8</v>
       </c>
@@ -742,7 +743,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -759,7 +760,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
@@ -774,7 +775,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="1" t="s">
         <v>8</v>
       </c>
@@ -789,7 +790,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -806,7 +807,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3"/>
+      <c r="A21" s="4"/>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
@@ -821,7 +822,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3"/>
+      <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>8</v>
       </c>
@@ -836,7 +837,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B23" s="5"/>
